--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_13-05-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_13-05-2025.xlsx
@@ -134,6 +134,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Price Tracker</author>
+  </authors>
+  <commentList>
+    <comment ref="L8" authorId="0" shapeId="0">
+      <text>
+        <t>£24.08</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>£30.00</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2855,5 +2875,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_13-05-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_13-05-2025.xlsx
@@ -134,26 +134,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Price Tracker</author>
-  </authors>
-  <commentList>
-    <comment ref="L8" authorId="0" shapeId="0">
-      <text>
-        <t>£24.08</t>
-      </text>
-    </comment>
-    <comment ref="L11" authorId="0" shapeId="0">
-      <text>
-        <t>£30.00</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -578,7 +558,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>£12.60</t>
+          <t>£11.40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -618,7 +598,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -675,7 +655,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>£14.46</t>
+          <t>£13.28</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -715,7 +695,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -752,17 +732,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£17.15</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£17.15</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -772,7 +752,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>£17.97</t>
+          <t>£16.83</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -812,7 +792,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -849,17 +829,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£18.22</t>
+          <t>£17.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£18.22</t>
+          <t>£17.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£18.22</t>
+          <t>£17.50</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -869,7 +849,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>£18.79</t>
+          <t>£17.93</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -909,7 +889,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -946,17 +926,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£23.11</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£23.11</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£23.11</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -966,7 +946,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>£24.26</t>
+          <t>£21.92</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1006,7 +986,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1043,17 +1023,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£24.68</t>
+          <t>£24.60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£24.68</t>
+          <t>£24.60</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£24.68</t>
+          <t>£24.60</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1063,7 +1043,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>£26.69</t>
+          <t>£23.64</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1103,7 +1083,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1140,17 +1120,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£25.00</t>
+          <t>£24.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£25.00</t>
+          <t>£24.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£25.00</t>
+          <t>£24.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1160,7 +1140,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>£26.74</t>
+          <t>£24.17</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1170,7 +1150,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£25.60</t>
+          <t>Error: list index out of range</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1200,7 +1180,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1237,17 +1217,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£28.97</t>
+          <t>£27.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£28.97</t>
+          <t>£27.00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£28.97</t>
+          <t>£27.00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1257,7 +1237,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>£30.33</t>
+          <t>£27.00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1297,7 +1277,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1334,17 +1314,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£31.95</t>
+          <t>£30.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£31.95</t>
+          <t>£30.50</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£31.95</t>
+          <t>£30.50</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1354,7 +1334,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>£33.37</t>
+          <t>£29.50</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1394,12 +1374,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1431,17 +1411,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£30.83</t>
+          <t>£29.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£30.83</t>
+          <t>£29.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£30.83</t>
+          <t>£29.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1451,7 +1431,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>£31.57</t>
+          <t>£30.42</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1491,7 +1471,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1528,52 +1508,52 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>£49.95</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>£38.06</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>£40.65</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>£37.14</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>**£51.20**-Sale Price old Price: £73.42</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>£40.65</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>No Link</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>£49.95</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>£42.12</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>£40.65</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>£37.14</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>**£51.20**-Sale Price old Price: £73.42</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>£40.65</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1583,12 +1563,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1598,7 +1578,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1608,7 +1588,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1625,17 +1605,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£37.57</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£37.57</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£37.57</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1645,7 +1625,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>£40.31</t>
+          <t>£36.46</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1660,7 +1640,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>**£43.99**-Sale Price old Price: £72.38</t>
+          <t>Error: list index out of range</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1685,7 +1665,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1722,17 +1702,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£45.53</t>
+          <t>£44.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£45.53</t>
+          <t>£44.00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1742,7 +1722,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>£48.06</t>
+          <t>£45.00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1782,7 +1762,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1802,7 +1782,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1819,29 +1799,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>£46.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>£46.00</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>£60.95</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>£46.88</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>£46.88</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>No Link</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>£60.95</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>£49.05</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>£46.80</t>
@@ -1879,7 +1859,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1899,7 +1879,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1916,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>£49.41</t>
+          <t>£45.68</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1976,7 +1956,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2023,67 +2003,67 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2093,7 +2073,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2120,17 +2100,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>£94.18</t>
+          <t>£106.38</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2140,12 +2120,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2155,7 +2135,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2165,22 +2145,22 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2217,17 +2197,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>£88.24</t>
+          <t>£93.15</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2237,12 +2217,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2252,7 +2232,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2262,22 +2242,22 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2314,42 +2294,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2359,27 +2339,27 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2411,42 +2391,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2456,27 +2436,27 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2508,42 +2488,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2553,27 +2533,27 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2610,12 +2590,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2625,12 +2605,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2645,7 +2625,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2655,7 +2635,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2665,7 +2645,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2707,12 +2687,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2722,12 +2702,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2742,7 +2722,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2752,7 +2732,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2762,7 +2742,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2804,12 +2784,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2819,12 +2799,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2839,7 +2819,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2849,7 +2829,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2859,7 +2839,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2875,6 +2855,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>